--- a/artfynd/A 54047-2023 artfynd.xlsx
+++ b/artfynd/A 54047-2023 artfynd.xlsx
@@ -1318,7 +1318,7 @@
         <v>117908285</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
